--- a/Team-Data/2011-12/4-14-2011-12.xlsx
+++ b/Team-Data/2011-12/4-14-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -775,16 +842,16 @@
         <v>25</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -796,13 +863,13 @@
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.583</v>
+        <v>0.576</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
         <v>77.09999999999999</v>
@@ -882,22 +949,22 @@
         <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="U3" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W3" t="n">
         <v>7.4</v>
@@ -912,19 +979,19 @@
         <v>20.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="n">
         <v>10</v>
@@ -933,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -960,34 +1027,34 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>24</v>
@@ -996,7 +1063,7 @@
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-13.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1151,13 +1218,13 @@
         <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1166,10 +1233,10 @@
         <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1321,7 +1388,7 @@
         <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.424</v>
+        <v>0.422</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.717</v>
+        <v>0.714</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
         <v>29.7</v>
       </c>
       <c r="T6" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U6" t="n">
         <v>20.4</v>
@@ -1452,22 +1519,22 @@
         <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1494,16 +1561,16 @@
         <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1515,10 +1582,10 @@
         <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>27</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1661,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
@@ -1688,7 +1755,7 @@
         <v>27</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
@@ -1861,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2013,28 +2080,28 @@
         <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2082,7 +2149,7 @@
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2117,49 +2184,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J10" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K10" t="n">
         <v>0.458</v>
       </c>
       <c r="L10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="O10" t="n">
         <v>14.8</v>
       </c>
       <c r="P10" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>29.3</v>
@@ -2180,22 +2247,22 @@
         <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA10" t="n">
         <v>16.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2210,13 +2277,13 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK10" t="n">
         <v>7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2243,7 +2310,7 @@
         <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2252,10 +2319,10 @@
         <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2407,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
         <v>19</v>
@@ -2431,7 +2498,7 @@
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
@@ -2449,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.633</v>
+        <v>0.627</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,49 +2566,49 @@
         <v>35.4</v>
       </c>
       <c r="J12" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L12" t="n">
         <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N12" t="n">
         <v>0.363</v>
       </c>
       <c r="O12" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P12" t="n">
         <v>26.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="V12" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.9</v>
@@ -2553,22 +2620,22 @@
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2577,10 +2644,10 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2598,13 +2665,13 @@
         <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2613,13 +2680,13 @@
         <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.617</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J13" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L13" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M13" t="n">
         <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
         <v>15.8</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.679</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>12.2</v>
@@ -2732,16 +2799,16 @@
         <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2762,7 +2829,7 @@
         <v>16</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2771,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
         <v>20</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
         <v>25</v>
@@ -2798,22 +2865,22 @@
         <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
         <v>22</v>
@@ -2998,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -3027,94 +3094,94 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
         <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.593</v>
+        <v>0.586</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M15" t="n">
         <v>12.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>0.326</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
         <v>12.5</v>
       </c>
       <c r="S15" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T15" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V15" t="n">
         <v>14.5</v>
       </c>
       <c r="W15" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH15" t="n">
         <v>14</v>
@@ -3123,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3135,16 +3202,16 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
@@ -3159,19 +3226,19 @@
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>6.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3308,7 +3375,7 @@
         <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>21</v>
@@ -3332,10 +3399,10 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
         <v>18</v>
@@ -3347,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3362,7 +3429,7 @@
         <v>4</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.492</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,34 +3476,34 @@
         <v>38.2</v>
       </c>
       <c r="J17" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.445</v>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
         <v>19.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O17" t="n">
         <v>16.1</v>
       </c>
       <c r="P17" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.774</v>
+        <v>0.778</v>
       </c>
       <c r="R17" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
         <v>41.9</v>
@@ -3445,13 +3512,13 @@
         <v>23.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
         <v>4.6</v>
@@ -3466,10 +3533,10 @@
         <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3493,22 +3560,22 @@
         <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
         <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
@@ -3523,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
@@ -3532,7 +3599,7 @@
         <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3544,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -3573,55 +3640,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.41</v>
+        <v>0.417</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M18" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O18" t="n">
         <v>19.4</v>
       </c>
       <c r="P18" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R18" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S18" t="n">
         <v>31.5</v>
       </c>
       <c r="T18" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U18" t="n">
         <v>19.6</v>
@@ -3633,7 +3700,7 @@
         <v>6.8</v>
       </c>
       <c r="X18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
@@ -3642,10 +3709,10 @@
         <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>-1.5</v>
@@ -3669,7 +3736,7 @@
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3690,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3714,7 +3781,7 @@
         <v>26</v>
       </c>
       <c r="AY18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ18" t="n">
         <v>8</v>
@@ -3723,7 +3790,7 @@
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,28 +3840,28 @@
         <v>34.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.425</v>
+        <v>0.426</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
         <v>22.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P19" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
@@ -3809,7 +3876,7 @@
         <v>20.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>7.6</v>
@@ -3818,19 +3885,19 @@
         <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z19" t="n">
         <v>19.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
@@ -3839,7 +3906,7 @@
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
         <v>24</v>
@@ -3848,7 +3915,7 @@
         <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
         <v>20</v>
@@ -3863,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -3896,16 +3963,16 @@
         <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4045,7 +4112,7 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -4060,7 +4127,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,7 +4136,7 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
@@ -4081,7 +4148,7 @@
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>15</v>
@@ -4209,7 +4276,7 @@
         <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,7 +4285,7 @@
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4242,7 +4309,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4251,7 +4318,7 @@
         <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
@@ -4263,13 +4330,13 @@
         <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,7 +4386,7 @@
         <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K22" t="n">
         <v>0.474</v>
@@ -4328,34 +4395,34 @@
         <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.803</v>
+        <v>0.801</v>
       </c>
       <c r="R22" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U22" t="n">
         <v>18.5</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
         <v>7.6</v>
@@ -4367,19 +4434,19 @@
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
       <c r="AC22" t="n">
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,16 +4458,16 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="n">
         <v>10</v>
@@ -4409,7 +4476,7 @@
         <v>12</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4433,7 +4500,7 @@
         <v>29</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW22" t="n">
         <v>17</v>
@@ -4454,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4561,22 +4628,22 @@
         <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF23" t="n">
         <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -4609,7 +4676,7 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4794,13 +4861,13 @@
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
@@ -4865,46 +4932,46 @@
         <v>37.6</v>
       </c>
       <c r="J25" t="n">
-        <v>82.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M25" t="n">
         <v>19.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O25" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P25" t="n">
         <v>21.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
         <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V25" t="n">
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X25" t="n">
         <v>5.6</v>
@@ -4919,22 +4986,22 @@
         <v>19.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
@@ -4943,22 +5010,22 @@
         <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>14</v>
       </c>
       <c r="AN25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4970,16 +5037,16 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
         <v>6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4997,7 +5064,7 @@
         <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,19 +5186,19 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK26" t="n">
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM26" t="n">
         <v>9</v>
@@ -5152,7 +5219,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5170,7 +5237,7 @@
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
@@ -5179,10 +5246,10 @@
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-6.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>27</v>
@@ -5322,19 +5389,19 @@
         <v>28</v>
       </c>
       <c r="AO27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP27" t="n">
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5361,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.724</v>
+        <v>0.719</v>
       </c>
       <c r="H28" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I28" t="n">
         <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,7 +5490,7 @@
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O28" t="n">
         <v>15.7</v>
@@ -5432,46 +5499,46 @@
         <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R28" t="n">
         <v>10.2</v>
       </c>
       <c r="S28" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U28" t="n">
         <v>22.6</v>
       </c>
       <c r="V28" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
         <v>101.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5510,25 +5577,25 @@
         <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG29" t="n">
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5692,13 +5759,13 @@
         <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>19</v>
@@ -5716,7 +5783,7 @@
         <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.508</v>
+        <v>0.517</v>
       </c>
       <c r="H30" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I30" t="n">
         <v>38.1</v>
@@ -5787,25 +5854,25 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="O30" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P30" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q30" t="n">
         <v>0.751</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S30" t="n">
         <v>30.7</v>
       </c>
       <c r="T30" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U30" t="n">
         <v>21.7</v>
@@ -5826,13 +5893,13 @@
         <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5871,7 +5938,7 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
@@ -5886,7 +5953,7 @@
         <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>0.233</v>
+        <v>0.237</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5957,7 +6024,7 @@
         <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.437</v>
@@ -5972,28 +6039,28 @@
         <v>0.321</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U31" t="n">
         <v>18.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.7</v>
@@ -6011,13 +6078,13 @@
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC31" t="n">
         <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6053,7 +6120,7 @@
         <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6062,16 +6129,16 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-14-2011-12</t>
+          <t>2012-04-14</t>
         </is>
       </c>
     </row>
